--- a/data/trans_orig/IP39B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP39B-Habitat-trans_orig.xlsx
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25132</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50507</t>
+          <t>50720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60630</t>
+          <t>60321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53338</t>
+          <t>53461</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63822</t>
+          <t>63551</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108364</t>
+          <t>108322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>122329</t>
+          <t>122332</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9994</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20548</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22637</t>
+          <t>23064</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23518</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39967</t>
+          <t>40134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78678</t>
+          <t>78938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90386</t>
+          <t>90585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77543</t>
+          <t>76617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90338</t>
+          <t>91038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>159751</t>
+          <t>159521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177861</t>
+          <t>177740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>525</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16046</t>
+          <t>15529</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>16930</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>29175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51537</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62213</t>
+          <t>62005</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>55608</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66643</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109778</t>
+          <t>110225</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125613</t>
+          <t>125313</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33310</t>
+          <t>32548</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22804</t>
+          <t>22600</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>31472</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51627</t>
+          <t>50771</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84242</t>
+          <t>84396</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>101113</t>
+          <t>100886</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102818</t>
+          <t>102860</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>116969</t>
+          <t>117003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>192199</t>
+          <t>192496</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>213753</t>
+          <t>214104</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>21663</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24799</t>
+          <t>25943</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>47013</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>71620</t>
+          <t>70260</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>45515</t>
+          <t>44917</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>67526</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>96963</t>
+          <t>97791</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>129354</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>278715</t>
+          <t>278170</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>303646</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>303552</t>
+          <t>302472</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>326633</t>
+          <t>327219</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>589580</t>
+          <t>588313</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>624468</t>
+          <t>623294</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>19345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>44229</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52389</t>
+          <t>52298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44185</t>
+          <t>43560</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53899</t>
+          <t>53880</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91345</t>
+          <t>91357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104431</t>
+          <t>104567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>568</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>18900</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30399</t>
+          <t>30878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63525</t>
+          <t>63786</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74960</t>
+          <t>74674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78863</t>
+          <t>78308</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89251</t>
+          <t>89181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146117</t>
+          <t>145081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161561</t>
+          <t>161333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>14797</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20441</t>
+          <t>19642</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30604</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52814</t>
+          <t>52782</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63116</t>
+          <t>63643</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47831</t>
+          <t>47984</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60155</t>
+          <t>60357</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>103935</t>
+          <t>105473</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>120945</t>
+          <t>121415</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,11%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18498</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>16240</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31592</t>
+          <t>32114</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77352</t>
+          <t>76367</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>90242</t>
+          <t>89849</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>77115</t>
+          <t>78163</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90445</t>
+          <t>90513</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>157817</t>
+          <t>158801</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>177224</t>
+          <t>177241</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>28138</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50564</t>
+          <t>50300</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>31409</t>
+          <t>31168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>50777</t>
+          <t>50792</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>67237</t>
+          <t>67471</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>94888</t>
+          <t>95253</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>249229</t>
+          <t>248741</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>271182</t>
+          <t>271594</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>262098</t>
+          <t>262097</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>284226</t>
+          <t>285319</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>517267</t>
+          <t>518936</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>551568</t>
+          <t>551817</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,47 +8257,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2196</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5835</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2196</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5916</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41580</t>
+          <t>41927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50333</t>
+          <t>50274</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55708</t>
+          <t>55654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63822</t>
+          <t>63934</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100147</t>
+          <t>100745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112700</t>
+          <t>113013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>553</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20216</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83147</t>
+          <t>83665</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91736</t>
+          <t>91624</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78809</t>
+          <t>78790</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90218</t>
+          <t>90490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165077</t>
+          <t>165869</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179473</t>
+          <t>179722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>550</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>547</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13611</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13208</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57494</t>
+          <t>57378</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67466</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66910</t>
+          <t>66453</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77081</t>
+          <t>77067</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126677</t>
+          <t>127177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>142169</t>
+          <t>142533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>22396</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18206</t>
+          <t>19140</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>20487</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36574</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>80455</t>
+          <t>80838</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>95474</t>
+          <t>94706</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95192</t>
+          <t>95700</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107620</t>
+          <t>107978</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>181000</t>
+          <t>180917</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>199707</t>
+          <t>199620</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18366</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25440</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46760</t>
+          <t>46838</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>23535</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>40474</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>57332</t>
+          <t>58119</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>84493</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>276656</t>
+          <t>274531</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>295781</t>
+          <t>295688</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>309397</t>
+          <t>308410</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>329914</t>
+          <t>331188</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>590035</t>
+          <t>588387</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>620637</t>
+          <t>620559</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
